--- a/光伏配储项目/电价数据/2026/广澳升压站.xlsx
+++ b/光伏配储项目/电价数据/2026/广澳升压站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.31412</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.28327</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.31611</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27456</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.26382</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.25378</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.24909</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.27219</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.26544</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.23758</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.14927</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14774</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.19101</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.28252</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07279000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.25736</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.08036</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17564</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26691</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.26979</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26982</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22105</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.30736</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.18989</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.27835</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.84765</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.51586</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.15059</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.07499</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7832899999999999</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.01907</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.99799</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.71562</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.9589800000000001</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.44669</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.43401</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.44901</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.04587</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.44927</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.43898</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.38413</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.32523</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.2194</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.28515</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.42875</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.27811</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.31202</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29143</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.09526000000000001</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.16888</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.61505</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.55304</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.14857</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.44215</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.13175</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.2985</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.1822</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.06257</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.2805299999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.26969</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.27486</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.6422899999999999</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.76605</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.73375</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.76488</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.27161</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.75698</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.76997</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.7573300000000001</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.9556699999999999</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.79827</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.5781000000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.77949</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.27205</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.77955</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7856300000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.77288</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.39412</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.74995</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.41906</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.32646</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.31385</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.31307</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.30753</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27456</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.28011</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.27529</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.27289</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.26729</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.27208</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.74674</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.75686</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.76593</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.22259</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.23366</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.12634</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.12497</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.18575</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.27901</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.4253</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.05415</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.49883</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.4936</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.48739</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.50459</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.43162</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.51139</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.25368</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.69225</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.4957</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.43997</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.39272</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.33089</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31581</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.45398</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48929</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.47888</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.04962</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.27158</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.8039700000000001</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.08142000000000001</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.06633</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.07808</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.27955</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.27241</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.18308</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.0861</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.07683</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66015</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5022799999999999</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30735</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.25593</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36307</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35295</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13344</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.01576</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.29817</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.28308</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26487</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25437</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.22993</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.09583</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.30564</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.27103</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.03202</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27488</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34788</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4107</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4241</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31835</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.07296</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30343</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.24737</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.25281</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.03641</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.06246</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19746</v>
+      </c>
+      <c r="L122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25459</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.05875</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.01811</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.25084</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21871</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19684</v>
+      </c>
+      <c r="W122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17888</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25202</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27311</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20573</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26868</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.04643</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.04782</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04789</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04924</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00423</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20173</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04451</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27129</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.18936</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.005690000000000001</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05479999999999999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05479999999999999</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14031</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31685</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30272</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.63744</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.16984</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22474</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.02431</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15669</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7694299999999999</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78099</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92031</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91412</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8630599999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29609</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88742</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63152</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18698</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8702799999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.65712</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33078</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03284</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53074</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5736599999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44999</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2071</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62191</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5384</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49776</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45589</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42432</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43721</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.41366</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37813</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38843</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44397</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.43169</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.45921</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.45747</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.26414</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.29648</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.60626</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87898</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.29177</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29168</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.20092</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.28926</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3056</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28606</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29472</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18381</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.2639</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26376</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27637</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26354</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27618</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29387</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32508</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.78322</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30882</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.29555</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.29772</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.29291</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.19842</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.191</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29858</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.27885</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.05544</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.05406</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.05983</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.27431</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.02093</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45017</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.10268</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.01002</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>-0.04491</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.04957</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>-0.03945000000000001</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>-0.04689</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.05967</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.21092</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.06652</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.06031</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.03204</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.08445</v>
+      </c>
+      <c r="U126" t="n">
+        <v>-0.02217</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.07704000000000001</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.25072</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.02466</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.19147</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.25603</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.13443</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.22923</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.05073</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.13337</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.23762</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.19052</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>-0.00525</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.01971</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.27384</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.23865</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.27776</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.24035</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.19994</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.18925</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.21146</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.03788</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.04788000000000001</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.10865</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.12374</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.04629</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.19697</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.05762</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.03365</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.01352</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.05196</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.09534000000000001</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.02361</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.19383</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.02732</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.23544</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.24329</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.25449</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.02702</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.04468</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.06254999999999999</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.06229999999999999</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.06017</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.06199</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.04604</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.05520000000000001</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.05479</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.04905</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.04633</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.06158</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.05707</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.06134000000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.06126</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.27699</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.07263</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.05797</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.23229</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.04621</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.22155</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.04831000000000001</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.0416</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.00915</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.0367</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19357</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.02086</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.19062</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.03459</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.04033</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.05067</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.04949</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.02413</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.04802</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.04094</v>
+      </c>
+      <c r="X127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.19546</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.0412</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.009179999999999999</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.00852</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.02185</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.04491</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.16186</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.01689</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.12886</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.01542</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.24735</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.00315</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.13313</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.0563</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.04649</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.04568999999999999</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.30108</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.11454</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.24445</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.04688000000000001</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.04264</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.1728</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.11759</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.04292</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.03647</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.16958</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.18944</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26543</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.22808</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.27794</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.28618</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.27368</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.21426</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.27813</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.26662</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.25287</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.28527</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.27329</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28682</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.27426</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.27161</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.27326</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.28422</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.27313</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.28811</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.27318</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.28556</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.39508</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.26331</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.26206</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.29053</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25346</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28446</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29766</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29692</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.28526</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.25525</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30196</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.26378</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.42913</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30516</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.31101</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.29139</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28896</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29283</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30152</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29658</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29726</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29834</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3442</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30758</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.01117</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.40587</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.62413</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.48071</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49933</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44412</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.48341</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42471</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.40271</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5415</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27817</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.16179</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.17334</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.39913</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.52703</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41447</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.41774</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.38111</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.08445999999999999</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.07395</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.41861</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.11904</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6033099999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.28896</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.30961</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.0673</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.45654</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.06336</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.10464</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.01668</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.05905</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.23885</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28747</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.27158</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.2758</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27942</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20475</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.19501</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.2685</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27749</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.26733</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.26703</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27529</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19772</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19526</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.16025</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23831</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.19526</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.20134</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20817</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.17417</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16559</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.16391</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.20144</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.23426</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.26188</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.24078</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.24097</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.24437</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.22347</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.27941</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.22313</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.22992</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29774</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.18999</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.23329</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.2698</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.23363</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.19403</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.04808</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.17919</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.19187</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.22415</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.24421</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.13497</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.24138</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.2703</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.22212</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.25805</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.30232</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.27064</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.27378</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28825</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.28846</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.27749</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.29058</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.2139</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29257</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.20742</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>-0.02056</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3187</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27629</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28571</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28696</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.2878500000000001</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27625</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28671</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.28282</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27641</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27637</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28675</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30164</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.5147200000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34148</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29926</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.3831</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41236</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40668</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.36827</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44502</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49853</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.58805</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5590599999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59435</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.74372</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46958</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.42893</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.31246</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4349</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42598</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32121</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.20806</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32797</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.00337</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.21166</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.2785899999999999</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.20053</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.26971</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.29154</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5395599999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6480199999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.32878</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41125</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27966</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.28116</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.28639</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.16709</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.28639</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.28659</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.17061</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.24568</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>-0.04867</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.04802</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.19919</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.19929</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>-0.0461</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.0378</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.19663</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.18994</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.19192</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.18987</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.26242</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.21421</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.07115</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.25848</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.03761</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.02949</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.16568</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.11037</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.16813</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.09651999999999999</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.17808</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.26804</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.17425</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.01399</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.2355</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.01116</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.01051</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.1738</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.20505</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17426</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.008029999999999999</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.16361</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.16585</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.16865</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.17146</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.006549999999999999</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.17426</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.00637</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.01772</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.18547</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18738</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.15582</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.04056</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.03913000000000001</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.1887</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.08946</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.12989</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.25696</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.25287</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.18661</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.16016</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.00209</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.19428</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.19078</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.12604</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.16868</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.14872</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.14923</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.01918</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.11175</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.01532</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22095</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.03994</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.25102</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.19815</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.22884</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.22514</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.09079000000000001</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.1007</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.22881</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.0709</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.01518</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.20776</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.23321</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.25213</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28187</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27768</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.05477000000000001</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.19228</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18899</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.27118</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.00017</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20784</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22805</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21811</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.04323</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.01312</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.00015</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.00015</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-7.000000000000001e-05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.20066</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.01362</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.00035</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.18071</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.01313</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.00094</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.00392</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24543</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.03628</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.006730000000000001</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-7.000000000000001e-05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02166</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02675</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03881</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04435</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.22382</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.09753000000000001</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.19968</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.20593</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.00039</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.17853</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29855</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28236</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25506</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29604</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.28225</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29149</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.24194</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.21271</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.27298</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.29498</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30592</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27179</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.03169</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.17662</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.17114</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.17557</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.17287</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.02151</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.16893</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.15737</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.02083</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.02294</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.0203</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.007730000000000001</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.009810000000000001</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.01369</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.84592</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85712</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.08459</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.00399</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.25523</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28384</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.04869</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00013</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29094</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06668</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30626</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47062</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.65164</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.50081</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.42538</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.73507</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.7902899999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.56337</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.4322</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.62214</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.7133400000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7133400000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.7122999999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.78889</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37645</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.43011</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.38828</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.31243</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.44088</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.26871</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.19947</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.26263</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25926</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.25101</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.22073</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.26797</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.20781</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.20333</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.16893</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.17134</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.0215</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.16702</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.18943</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.23918</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.27099</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.26926</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.22041</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.23841</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.2835299999999999</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.2276</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.26307</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26899</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32656</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37207</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.40419</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29527</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29638</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.2033</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.3242</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32493</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32293</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.44679</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41161</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.45779</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.27658</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.72937</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.74739</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40842</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.49976</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.64897</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.7487</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.41063</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42375</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31983</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33026</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.37489</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33669</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36359</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.58992</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.39303</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.76034</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.6652899999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5556</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32675</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28576</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.02023</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.29621</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29496</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28731</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19564</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.4143</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.53018</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.15143</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.20307</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.47201</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.33219</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.66383</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40627</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34091</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.19996</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.32392</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.04844</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.04085</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>-0.0044</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.13854</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.34163</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="E143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33836</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17909</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29704</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14638</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.20101</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14204</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.11621</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22592</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26665</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14598</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14331</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28753</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.1885</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.26716</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.09254000000000001</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.19829</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.02073</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.22018</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.14201</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23801</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.28497</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.17679</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.15039</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.08408</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.4164</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39001</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.04604999999999999</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>-0.006889999999999999</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>-0.00449</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.28211</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.03894</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.26424</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.0614</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.04409</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.28549</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.33292</v>
       </c>
     </row>
   </sheetData>
